--- a/results/reliability_eval/Llama-3-8B_P1376_sample_15_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P1376_sample_15_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5797233325452635</v>
+        <v>0.455664190633399</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8184125010643337</v>
+        <v>0.8161528017804635</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5795034061106561</v>
+        <v>0.455664190633399</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8182377613758646</v>
+        <v>0.8161528017804635</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4190945628687204</v>
+        <v>0.5610119992381436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7268062088406571</v>
+        <v>0.8729832028790507</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9971162146262075</v>
+        <v>0.9979225304918913</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9988275071371554</v>
+        <v>0.9993917012791717</v>
       </c>
       <c r="I2" t="n">
-        <v>0.761</v>
+        <v>0.829</v>
       </c>
     </row>
   </sheetData>
